--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_ANTLERLESS.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_ANTLERLESS.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N207"/>
+  <dimension ref="A1:O207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -669,7 +675,8 @@
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -737,7 +744,8 @@
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -805,7 +813,8 @@
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -872,8 +881,13 @@
           <t>49.2</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -941,7 +955,8 @@
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -1009,7 +1024,8 @@
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -1077,7 +1093,8 @@
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -1145,7 +1162,8 @@
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
@@ -1212,8 +1230,13 @@
           <t>44.5</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -1280,8 +1303,13 @@
           <t>34.9</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -1348,8 +1376,13 @@
           <t>35.5</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -1416,8 +1449,13 @@
           <t>62.8</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -1484,8 +1522,13 @@
           <t>38.5</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -1553,7 +1596,8 @@
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -1620,8 +1664,13 @@
           <t>31.7</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -1688,8 +1737,13 @@
           <t>48.9</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -1757,7 +1811,8 @@
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
@@ -1825,7 +1880,8 @@
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -1892,8 +1948,13 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -1960,8 +2021,13 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr">
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2028,8 +2094,13 @@
           <t>35.2</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -2097,7 +2168,8 @@
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2164,8 +2236,13 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -2232,8 +2309,13 @@
           <t>71.1</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -2300,8 +2382,13 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -2368,8 +2455,13 @@
           <t>32.5</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2436,8 +2528,13 @@
           <t>16.7</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -2504,8 +2601,13 @@
           <t>28.6</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="6" t="inlineStr">
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2573,7 +2675,8 @@
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2641,7 +2744,8 @@
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="6" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -2708,8 +2812,13 @@
           <t>63.6</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -2776,8 +2885,13 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr">
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="6" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -2845,7 +2959,8 @@
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -2913,7 +3028,8 @@
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="6" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -2981,7 +3097,8 @@
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr"/>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -3048,8 +3165,13 @@
           <t>36.8</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr"/>
-      <c r="N39" s="6" t="inlineStr">
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -3116,8 +3238,13 @@
           <t>93.3</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -3184,8 +3311,13 @@
           <t>77.6</t>
         </is>
       </c>
-      <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="6" t="inlineStr">
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -3252,8 +3384,13 @@
           <t>39.1</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3320,8 +3457,13 @@
           <t>51.4</t>
         </is>
       </c>
-      <c r="M43" s="6" t="inlineStr"/>
-      <c r="N43" s="6" t="inlineStr">
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" s="6" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -3388,8 +3530,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3456,8 +3603,13 @@
           <t>13.2</t>
         </is>
       </c>
-      <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="6" t="inlineStr">
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -3524,8 +3676,13 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr"/>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -3592,8 +3749,13 @@
           <t>21.7</t>
         </is>
       </c>
-      <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr">
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -3660,8 +3822,13 @@
           <t>24.4</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -3728,8 +3895,13 @@
           <t>47.1</t>
         </is>
       </c>
-      <c r="M49" s="6" t="inlineStr"/>
-      <c r="N49" s="6" t="inlineStr">
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -3796,8 +3968,13 @@
           <t>69.1</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3865,7 +4042,8 @@
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="6" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3932,8 +4110,13 @@
           <t>31.6</t>
         </is>
       </c>
-      <c r="M52" s="4" t="inlineStr"/>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -4000,8 +4183,13 @@
           <t>6.3</t>
         </is>
       </c>
-      <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr">
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -4068,8 +4256,13 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr"/>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -4136,8 +4329,13 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="6" t="inlineStr">
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" s="6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -4204,8 +4402,13 @@
           <t>47.4</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -4273,7 +4476,8 @@
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="6" t="inlineStr">
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -4341,7 +4545,8 @@
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -4409,7 +4614,8 @@
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="6" t="inlineStr">
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" s="6" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -4477,7 +4683,8 @@
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4545,7 +4752,8 @@
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="6" t="inlineStr">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" s="6" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
@@ -4613,7 +4821,8 @@
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -4681,7 +4890,8 @@
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr">
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -4749,7 +4959,8 @@
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr"/>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
@@ -4817,7 +5028,8 @@
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr">
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -4885,7 +5097,8 @@
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr"/>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -4953,7 +5166,8 @@
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="6" t="inlineStr">
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" s="6" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -5021,7 +5235,8 @@
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -5089,7 +5304,8 @@
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr">
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -5157,7 +5373,8 @@
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -5225,7 +5442,8 @@
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="6" t="inlineStr">
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -5293,7 +5511,8 @@
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr"/>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
@@ -5361,7 +5580,8 @@
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="6" t="inlineStr">
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" s="6" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -5429,7 +5649,8 @@
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr"/>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -5497,7 +5718,8 @@
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="6" t="inlineStr">
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" s="6" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
@@ -5565,7 +5787,8 @@
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr"/>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -5633,7 +5856,8 @@
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="6" t="inlineStr">
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" s="6" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -5701,7 +5925,8 @@
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr"/>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -5769,7 +5994,8 @@
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="6" t="inlineStr">
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" s="6" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -5837,7 +6063,8 @@
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr"/>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -5905,7 +6132,8 @@
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr"/>
-      <c r="N81" s="6" t="inlineStr">
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" s="6" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -5973,7 +6201,8 @@
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr"/>
-      <c r="N82" s="4" t="inlineStr">
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -6041,7 +6270,8 @@
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr"/>
-      <c r="N83" s="6" t="inlineStr">
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -6109,7 +6339,8 @@
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr"/>
-      <c r="N84" s="4" t="inlineStr">
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -6177,7 +6408,8 @@
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="6" t="inlineStr">
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" s="6" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -6245,7 +6477,8 @@
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr"/>
-      <c r="N86" s="4" t="inlineStr">
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -6313,7 +6546,8 @@
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr"/>
-      <c r="N87" s="6" t="inlineStr">
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -6381,7 +6615,8 @@
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr"/>
-      <c r="N88" s="4" t="inlineStr">
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" s="4" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
@@ -6449,7 +6684,8 @@
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr"/>
-      <c r="N89" s="6" t="inlineStr">
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" s="6" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -6517,7 +6753,8 @@
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr"/>
-      <c r="N90" s="4" t="inlineStr">
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -6585,7 +6822,8 @@
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr"/>
-      <c r="N91" s="6" t="inlineStr">
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" s="6" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
@@ -6653,7 +6891,8 @@
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr"/>
-      <c r="N92" s="4" t="inlineStr">
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -6721,7 +6960,8 @@
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr"/>
-      <c r="N93" s="6" t="inlineStr">
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -6789,7 +7029,8 @@
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr"/>
-      <c r="N94" s="4" t="inlineStr">
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
@@ -6857,7 +7098,8 @@
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr"/>
-      <c r="N95" s="6" t="inlineStr">
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" s="6" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -6925,7 +7167,8 @@
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr"/>
-      <c r="N96" s="4" t="inlineStr">
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" s="4" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
@@ -6993,7 +7236,8 @@
         </is>
       </c>
       <c r="M97" s="6" t="inlineStr"/>
-      <c r="N97" s="6" t="inlineStr">
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -7061,7 +7305,8 @@
         </is>
       </c>
       <c r="M98" s="4" t="inlineStr"/>
-      <c r="N98" s="4" t="inlineStr">
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -7129,7 +7374,8 @@
         </is>
       </c>
       <c r="M99" s="6" t="inlineStr"/>
-      <c r="N99" s="6" t="inlineStr">
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -7197,7 +7443,8 @@
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr">
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" s="4" t="inlineStr">
         <is>
           <t>11.5</t>
         </is>
@@ -7265,7 +7512,8 @@
         </is>
       </c>
       <c r="M101" s="6" t="inlineStr"/>
-      <c r="N101" s="6" t="inlineStr">
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" s="6" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -7333,7 +7581,8 @@
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr"/>
-      <c r="N102" s="4" t="inlineStr">
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" s="4" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -7401,7 +7650,8 @@
         </is>
       </c>
       <c r="M103" s="6" t="inlineStr"/>
-      <c r="N103" s="6" t="inlineStr">
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" s="6" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
@@ -7457,7 +7707,8 @@
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr">
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7524,8 +7775,13 @@
           <t>8.3</t>
         </is>
       </c>
-      <c r="M105" s="6" t="inlineStr"/>
-      <c r="N105" s="6" t="inlineStr">
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" s="6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -7592,8 +7848,13 @@
           <t>13.8</t>
         </is>
       </c>
-      <c r="M106" s="4" t="inlineStr"/>
-      <c r="N106" s="4" t="inlineStr">
+      <c r="M106" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -7661,7 +7922,8 @@
         </is>
       </c>
       <c r="M107" s="6" t="inlineStr"/>
-      <c r="N107" s="6" t="inlineStr">
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -7729,7 +7991,8 @@
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr"/>
-      <c r="N108" s="4" t="inlineStr">
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -7796,8 +8059,13 @@
           <t>24.7</t>
         </is>
       </c>
-      <c r="M109" s="6" t="inlineStr"/>
-      <c r="N109" s="6" t="inlineStr">
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -7865,7 +8133,8 @@
         </is>
       </c>
       <c r="M110" s="4" t="inlineStr"/>
-      <c r="N110" s="4" t="inlineStr">
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -7933,7 +8202,8 @@
         </is>
       </c>
       <c r="M111" s="6" t="inlineStr"/>
-      <c r="N111" s="6" t="inlineStr">
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" s="6" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -8001,7 +8271,8 @@
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr">
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -8068,8 +8339,13 @@
           <t>40</t>
         </is>
       </c>
-      <c r="M113" s="6" t="inlineStr"/>
-      <c r="N113" s="6" t="inlineStr">
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" s="6" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -8136,8 +8412,13 @@
           <t>40</t>
         </is>
       </c>
-      <c r="M114" s="4" t="inlineStr"/>
-      <c r="N114" s="4" t="inlineStr">
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" s="4" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -8205,7 +8486,8 @@
         </is>
       </c>
       <c r="M115" s="6" t="inlineStr"/>
-      <c r="N115" s="6" t="inlineStr">
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" s="6" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -8273,7 +8555,8 @@
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr"/>
-      <c r="N116" s="4" t="inlineStr">
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -8340,8 +8623,13 @@
           <t>45.9</t>
         </is>
       </c>
-      <c r="M117" s="6" t="inlineStr"/>
-      <c r="N117" s="6" t="inlineStr">
+      <c r="M117" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -8408,8 +8696,13 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="M118" s="4" t="inlineStr"/>
-      <c r="N118" s="4" t="inlineStr">
+      <c r="M118" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" s="4" t="inlineStr">
         <is>
           <t>14.5</t>
         </is>
@@ -8476,8 +8769,13 @@
           <t>26</t>
         </is>
       </c>
-      <c r="M119" s="6" t="inlineStr"/>
-      <c r="N119" s="6" t="inlineStr">
+      <c r="M119" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" s="6" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
@@ -8528,8 +8826,13 @@
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr"/>
-      <c r="M120" s="4" t="inlineStr"/>
-      <c r="N120" s="4" t="inlineStr"/>
+      <c r="M120" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" s="4" t="inlineStr"/>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
@@ -8581,7 +8884,8 @@
         </is>
       </c>
       <c r="M121" s="6" t="inlineStr"/>
-      <c r="N121" s="6" t="inlineStr">
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -8648,8 +8952,13 @@
           <t>42.3</t>
         </is>
       </c>
-      <c r="M122" s="4" t="inlineStr"/>
-      <c r="N122" s="4" t="inlineStr">
+      <c r="M122" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" s="4" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -8716,8 +9025,13 @@
           <t>37.9</t>
         </is>
       </c>
-      <c r="M123" s="6" t="inlineStr"/>
-      <c r="N123" s="6" t="inlineStr">
+      <c r="M123" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -8784,8 +9098,13 @@
           <t>57.6</t>
         </is>
       </c>
-      <c r="M124" s="4" t="inlineStr"/>
-      <c r="N124" s="4" t="inlineStr">
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -8852,8 +9171,13 @@
           <t>78.1</t>
         </is>
       </c>
-      <c r="M125" s="6" t="inlineStr"/>
-      <c r="N125" s="6" t="inlineStr">
+      <c r="M125" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" s="6" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -8921,7 +9245,8 @@
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr"/>
-      <c r="N126" s="4" t="inlineStr">
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -8989,7 +9314,8 @@
         </is>
       </c>
       <c r="M127" s="6" t="inlineStr"/>
-      <c r="N127" s="6" t="inlineStr">
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" s="6" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -9057,7 +9383,8 @@
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr"/>
-      <c r="N128" s="4" t="inlineStr">
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -9124,8 +9451,13 @@
           <t>32.5</t>
         </is>
       </c>
-      <c r="M129" s="6" t="inlineStr"/>
-      <c r="N129" s="6" t="inlineStr">
+      <c r="M129" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" s="6" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -9193,7 +9525,8 @@
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr"/>
-      <c r="N130" s="4" t="inlineStr">
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -9261,7 +9594,8 @@
         </is>
       </c>
       <c r="M131" s="6" t="inlineStr"/>
-      <c r="N131" s="6" t="inlineStr">
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" s="6" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
@@ -9329,7 +9663,8 @@
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr"/>
-      <c r="N132" s="4" t="inlineStr">
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -9397,7 +9732,8 @@
         </is>
       </c>
       <c r="M133" s="6" t="inlineStr"/>
-      <c r="N133" s="6" t="inlineStr">
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" s="6" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -9464,8 +9800,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="M134" s="4" t="inlineStr"/>
-      <c r="N134" s="4" t="inlineStr">
+      <c r="M134" s="4" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" s="4" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -9532,8 +9873,13 @@
           <t>34.9</t>
         </is>
       </c>
-      <c r="M135" s="6" t="inlineStr"/>
-      <c r="N135" s="6" t="inlineStr">
+      <c r="M135" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -9600,8 +9946,13 @@
           <t>47.7</t>
         </is>
       </c>
-      <c r="M136" s="4" t="inlineStr"/>
-      <c r="N136" s="4" t="inlineStr">
+      <c r="M136" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" s="4" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
@@ -9668,8 +10019,13 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="M137" s="6" t="inlineStr"/>
-      <c r="N137" s="6" t="inlineStr">
+      <c r="M137" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" s="6" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -9736,8 +10092,13 @@
           <t>40</t>
         </is>
       </c>
-      <c r="M138" s="4" t="inlineStr"/>
-      <c r="N138" s="4" t="inlineStr">
+      <c r="M138" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" s="4" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -9804,8 +10165,13 @@
           <t>17.4</t>
         </is>
       </c>
-      <c r="M139" s="6" t="inlineStr"/>
-      <c r="N139" s="6" t="inlineStr">
+      <c r="M139" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -9872,8 +10238,13 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="M140" s="4" t="inlineStr"/>
-      <c r="N140" s="4" t="inlineStr">
+      <c r="M140" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -9940,8 +10311,13 @@
           <t>28.6</t>
         </is>
       </c>
-      <c r="M141" s="6" t="inlineStr"/>
-      <c r="N141" s="6" t="inlineStr">
+      <c r="M141" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -10008,8 +10384,13 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M142" s="4" t="inlineStr"/>
-      <c r="N142" s="4" t="inlineStr">
+      <c r="M142" s="4" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -10077,7 +10458,8 @@
         </is>
       </c>
       <c r="M143" s="6" t="inlineStr"/>
-      <c r="N143" s="6" t="inlineStr">
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" s="6" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
@@ -10145,7 +10527,8 @@
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr"/>
-      <c r="N144" s="4" t="inlineStr">
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" s="4" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -10213,7 +10596,8 @@
         </is>
       </c>
       <c r="M145" s="6" t="inlineStr"/>
-      <c r="N145" s="6" t="inlineStr">
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" s="6" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -10264,8 +10648,13 @@
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr"/>
-      <c r="M146" s="4" t="inlineStr"/>
-      <c r="N146" s="4" t="inlineStr"/>
+      <c r="M146" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" s="4" t="inlineStr"/>
     </row>
     <row r="147" ht="24" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
@@ -10328,8 +10717,13 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M147" s="6" t="inlineStr"/>
-      <c r="N147" s="6" t="inlineStr">
+      <c r="M147" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" s="6" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -10397,7 +10791,8 @@
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr"/>
-      <c r="N148" s="4" t="inlineStr">
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -10465,7 +10860,8 @@
         </is>
       </c>
       <c r="M149" s="6" t="inlineStr"/>
-      <c r="N149" s="6" t="inlineStr">
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" s="6" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
@@ -10533,7 +10929,8 @@
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr"/>
-      <c r="N150" s="4" t="inlineStr">
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -10601,7 +10998,8 @@
         </is>
       </c>
       <c r="M151" s="6" t="inlineStr"/>
-      <c r="N151" s="6" t="inlineStr">
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" s="6" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -10669,7 +11067,8 @@
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr"/>
-      <c r="N152" s="4" t="inlineStr">
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" s="4" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -10737,7 +11136,8 @@
         </is>
       </c>
       <c r="M153" s="6" t="inlineStr"/>
-      <c r="N153" s="6" t="inlineStr">
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" s="6" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -10805,7 +11205,8 @@
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr"/>
-      <c r="N154" s="4" t="inlineStr">
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -10873,7 +11274,8 @@
         </is>
       </c>
       <c r="M155" s="6" t="inlineStr"/>
-      <c r="N155" s="6" t="inlineStr">
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" s="6" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -10941,7 +11343,8 @@
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr"/>
-      <c r="N156" s="4" t="inlineStr">
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -10997,7 +11400,8 @@
         </is>
       </c>
       <c r="M157" s="6" t="inlineStr"/>
-      <c r="N157" s="6" t="inlineStr">
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" s="6" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -11053,7 +11457,8 @@
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr"/>
-      <c r="N158" s="4" t="inlineStr">
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" s="4" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -11121,7 +11526,8 @@
         </is>
       </c>
       <c r="M159" s="6" t="inlineStr"/>
-      <c r="N159" s="6" t="inlineStr">
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -11188,8 +11594,13 @@
           <t>82.6</t>
         </is>
       </c>
-      <c r="M160" s="4" t="inlineStr"/>
-      <c r="N160" s="4" t="inlineStr">
+      <c r="M160" s="4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -11256,8 +11667,13 @@
           <t>5.3</t>
         </is>
       </c>
-      <c r="M161" s="6" t="inlineStr"/>
-      <c r="N161" s="6" t="inlineStr">
+      <c r="M161" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -11325,7 +11741,8 @@
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr"/>
-      <c r="N162" s="4" t="inlineStr">
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -11392,8 +11809,13 @@
           <t>62.5</t>
         </is>
       </c>
-      <c r="M163" s="6" t="inlineStr"/>
-      <c r="N163" s="6" t="inlineStr">
+      <c r="M163" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" s="6" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -11461,7 +11883,8 @@
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr"/>
-      <c r="N164" s="4" t="inlineStr">
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -11529,7 +11952,8 @@
         </is>
       </c>
       <c r="M165" s="6" t="inlineStr"/>
-      <c r="N165" s="6" t="inlineStr">
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" s="6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -11597,7 +12021,8 @@
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr"/>
-      <c r="N166" s="4" t="inlineStr">
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -11665,7 +12090,8 @@
         </is>
       </c>
       <c r="M167" s="6" t="inlineStr"/>
-      <c r="N167" s="6" t="inlineStr">
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -11729,7 +12155,8 @@
       </c>
       <c r="L168" s="4" t="inlineStr"/>
       <c r="M168" s="4" t="inlineStr"/>
-      <c r="N168" s="4" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" s="4" t="inlineStr"/>
     </row>
     <row r="169" ht="24" customHeight="1">
       <c r="A169" s="5" t="inlineStr">
@@ -11792,8 +12219,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="M169" s="6" t="inlineStr"/>
-      <c r="N169" s="6" t="inlineStr">
+      <c r="M169" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -11860,8 +12292,13 @@
           <t>14.8</t>
         </is>
       </c>
-      <c r="M170" s="4" t="inlineStr"/>
-      <c r="N170" s="4" t="inlineStr">
+      <c r="M170" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -11928,8 +12365,13 @@
           <t>61.3</t>
         </is>
       </c>
-      <c r="M171" s="6" t="inlineStr"/>
-      <c r="N171" s="6" t="inlineStr">
+      <c r="M171" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" s="6" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -11984,8 +12426,13 @@
           <t>60</t>
         </is>
       </c>
-      <c r="M172" s="4" t="inlineStr"/>
-      <c r="N172" s="4" t="inlineStr">
+      <c r="M172" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -12041,7 +12488,8 @@
         </is>
       </c>
       <c r="M173" s="6" t="inlineStr"/>
-      <c r="N173" s="6" t="inlineStr">
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -12101,7 +12549,8 @@
         </is>
       </c>
       <c r="M174" s="4" t="inlineStr"/>
-      <c r="N174" s="4" t="inlineStr">
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" s="4" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -12161,7 +12610,8 @@
         </is>
       </c>
       <c r="M175" s="6" t="inlineStr"/>
-      <c r="N175" s="6" t="inlineStr">
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" s="6" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
@@ -12221,7 +12671,8 @@
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr"/>
-      <c r="N176" s="4" t="inlineStr">
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" s="4" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -12280,8 +12731,13 @@
           <t>53.5</t>
         </is>
       </c>
-      <c r="M177" s="6" t="inlineStr"/>
-      <c r="N177" s="6" t="inlineStr">
+      <c r="M177" s="6" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -12340,8 +12796,13 @@
           <t>46.7</t>
         </is>
       </c>
-      <c r="M178" s="4" t="inlineStr"/>
-      <c r="N178" s="4" t="inlineStr">
+      <c r="M178" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" s="4" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -12400,8 +12861,13 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="M179" s="6" t="inlineStr"/>
-      <c r="N179" s="6" t="inlineStr">
+      <c r="M179" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" s="6" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -12460,8 +12926,13 @@
           <t>27.8</t>
         </is>
       </c>
-      <c r="M180" s="4" t="inlineStr"/>
-      <c r="N180" s="4" t="inlineStr">
+      <c r="M180" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -12520,8 +12991,13 @@
           <t>26.2</t>
         </is>
       </c>
-      <c r="M181" s="6" t="inlineStr"/>
-      <c r="N181" s="6" t="inlineStr">
+      <c r="M181" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" s="6" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
@@ -12580,8 +13056,13 @@
           <t>41.6</t>
         </is>
       </c>
-      <c r="M182" s="4" t="inlineStr"/>
-      <c r="N182" s="4" t="inlineStr">
+      <c r="M182" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" s="4" t="inlineStr">
         <is>
           <t>9.7</t>
         </is>
@@ -12640,8 +13121,13 @@
           <t>53.1</t>
         </is>
       </c>
-      <c r="M183" s="6" t="inlineStr"/>
-      <c r="N183" s="6" t="inlineStr">
+      <c r="M183" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" s="6" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -12700,8 +13186,13 @@
           <t>37.8</t>
         </is>
       </c>
-      <c r="M184" s="4" t="inlineStr"/>
-      <c r="N184" s="4" t="inlineStr">
+      <c r="M184" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" s="4" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
@@ -12760,8 +13251,13 @@
           <t>40.9</t>
         </is>
       </c>
-      <c r="M185" s="6" t="inlineStr"/>
-      <c r="N185" s="6" t="inlineStr">
+      <c r="M185" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" s="6" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -12820,8 +13316,13 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M186" s="4" t="inlineStr"/>
-      <c r="N186" s="4" t="inlineStr">
+      <c r="M186" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" s="4" t="inlineStr">
         <is>
           <t>9.8</t>
         </is>
@@ -12880,8 +13381,13 @@
           <t>36.7</t>
         </is>
       </c>
-      <c r="M187" s="6" t="inlineStr"/>
-      <c r="N187" s="6" t="inlineStr">
+      <c r="M187" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" s="6" t="inlineStr">
         <is>
           <t>11.4</t>
         </is>
@@ -12940,8 +13446,13 @@
           <t>60</t>
         </is>
       </c>
-      <c r="M188" s="4" t="inlineStr"/>
-      <c r="N188" s="4" t="inlineStr">
+      <c r="M188" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -13000,8 +13511,13 @@
           <t>48.1</t>
         </is>
       </c>
-      <c r="M189" s="6" t="inlineStr"/>
-      <c r="N189" s="6" t="inlineStr">
+      <c r="M189" s="6" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" s="6" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
@@ -13060,8 +13576,13 @@
           <t>30</t>
         </is>
       </c>
-      <c r="M190" s="4" t="inlineStr"/>
-      <c r="N190" s="4" t="inlineStr">
+      <c r="M190" s="4" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" s="4" t="inlineStr">
         <is>
           <t>13.7</t>
         </is>
@@ -13121,7 +13642,8 @@
         </is>
       </c>
       <c r="M191" s="6" t="inlineStr"/>
-      <c r="N191" s="6" t="inlineStr">
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" s="6" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
@@ -13180,8 +13702,13 @@
           <t>21.4</t>
         </is>
       </c>
-      <c r="M192" s="4" t="inlineStr"/>
-      <c r="N192" s="4" t="inlineStr">
+      <c r="M192" s="4" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" s="4" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -13241,7 +13768,8 @@
         </is>
       </c>
       <c r="M193" s="6" t="inlineStr"/>
-      <c r="N193" s="6" t="inlineStr">
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" s="6" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -13301,7 +13829,8 @@
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr"/>
-      <c r="N194" s="4" t="inlineStr">
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" s="4" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -13360,8 +13889,13 @@
           <t>42.4</t>
         </is>
       </c>
-      <c r="M195" s="6" t="inlineStr"/>
-      <c r="N195" s="6" t="inlineStr">
+      <c r="M195" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" s="6" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -13420,8 +13954,13 @@
           <t>34.7</t>
         </is>
       </c>
-      <c r="M196" s="4" t="inlineStr"/>
-      <c r="N196" s="4" t="inlineStr">
+      <c r="M196" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" s="4" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -13480,8 +14019,13 @@
           <t>53.7</t>
         </is>
       </c>
-      <c r="M197" s="6" t="inlineStr"/>
-      <c r="N197" s="6" t="inlineStr">
+      <c r="M197" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -13549,7 +14093,8 @@
         </is>
       </c>
       <c r="M198" s="4" t="inlineStr"/>
-      <c r="N198" s="4" t="inlineStr">
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" s="4" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -13617,7 +14162,8 @@
         </is>
       </c>
       <c r="M199" s="6" t="inlineStr"/>
-      <c r="N199" s="6" t="inlineStr">
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" s="6" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -13684,8 +14230,13 @@
           <t>91.4</t>
         </is>
       </c>
-      <c r="M200" s="4" t="inlineStr"/>
-      <c r="N200" s="4" t="inlineStr">
+      <c r="M200" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -13752,8 +14303,13 @@
           <t>17.8</t>
         </is>
       </c>
-      <c r="M201" s="6" t="inlineStr"/>
-      <c r="N201" s="6" t="inlineStr">
+      <c r="M201" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" s="6" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -13820,8 +14376,13 @@
           <t>13.4</t>
         </is>
       </c>
-      <c r="M202" s="4" t="inlineStr"/>
-      <c r="N202" s="4" t="inlineStr">
+      <c r="M202" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" s="4" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -13880,8 +14441,13 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="M203" s="6" t="inlineStr"/>
-      <c r="N203" s="6" t="inlineStr">
+      <c r="M203" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" s="6" t="inlineStr">
         <is>
           <t>11.7</t>
         </is>
@@ -13941,7 +14507,8 @@
         </is>
       </c>
       <c r="M204" s="4" t="inlineStr"/>
-      <c r="N204" s="4" t="inlineStr">
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" s="4" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
@@ -13993,7 +14560,8 @@
       </c>
       <c r="L205" s="6" t="inlineStr"/>
       <c r="M205" s="6" t="inlineStr"/>
-      <c r="N205" s="6" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" s="6" t="inlineStr"/>
     </row>
     <row r="206" ht="32" customHeight="1">
       <c r="A206" s="3" t="inlineStr">
@@ -14045,7 +14613,8 @@
         </is>
       </c>
       <c r="M206" s="4" t="inlineStr"/>
-      <c r="N206" s="4" t="inlineStr">
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -14105,7 +14674,8 @@
         </is>
       </c>
       <c r="M207" s="6" t="inlineStr"/>
-      <c r="N207" s="6" t="inlineStr">
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
